--- a/excel/Shipping.xlsx
+++ b/excel/Shipping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\Power-BI\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA00777D-9E93-4C1C-85BE-39CC0127CAC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E5FB34-AEDD-4187-B5C1-104170A65544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{DC5D127A-DB37-42F5-8ABD-17131823F8D0}"/>
   </bookViews>
@@ -771,6 +771,9 @@
       <c r="C6" s="1">
         <v>45670</v>
       </c>
+      <c r="D6" s="1">
+        <v>45672</v>
+      </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
@@ -852,6 +855,12 @@
       <c r="B9" t="s">
         <v>38</v>
       </c>
+      <c r="C9" s="1">
+        <v>45677</v>
+      </c>
+      <c r="D9" s="1">
+        <v>45681</v>
+      </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
@@ -936,6 +945,9 @@
       <c r="C12" s="1">
         <v>45691</v>
       </c>
+      <c r="D12" s="1">
+        <v>45687</v>
+      </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
@@ -1135,6 +1147,9 @@
       </c>
       <c r="C19" s="1">
         <v>45712</v>
+      </c>
+      <c r="D19" s="1">
+        <v>45713</v>
       </c>
       <c r="E19" t="s">
         <v>11</v>
